--- a/shift_report_forms/002_shift_handoff_preferences_survey--shift_report_forms.xlsx
+++ b/shift_report_forms/002_shift_handoff_preferences_survey--shift_report_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -780,8 +780,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -809,12 +809,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -826,12 +826,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'primary'}</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Primary'}</t>
+          <t>Primary</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'secondary'}</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Secondary'}</t>
+          <t>Secondary</t>
         </is>
       </c>
     </row>
@@ -860,12 +860,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -877,12 +877,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'voice'}</t>
+          <t>voice</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Voice'}</t>
+          <t>Voice</t>
         </is>
       </c>
     </row>
@@ -894,12 +894,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'video'}</t>
+          <t>video</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Video'}</t>
+          <t>Video</t>
         </is>
       </c>
     </row>
@@ -911,12 +911,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'text'}</t>
+          <t>text</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Text'}</t>
+          <t>Text</t>
         </is>
       </c>
     </row>
@@ -928,12 +928,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -945,12 +945,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -962,12 +962,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'bi-weekly'}</t>
+          <t>bi-weekly</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Bi-Weekly'}</t>
+          <t>Bi-Weekly</t>
         </is>
       </c>
     </row>
@@ -996,12 +996,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1013,12 +1013,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'prophets'}</t>
+          <t>prophets</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Prophets'}</t>
+          <t>Prophets</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'shift_leader'}</t>
+          <t>shift_leader</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Shift Leader'}</t>
+          <t>Shift Leader</t>
         </is>
       </c>
     </row>
@@ -1047,12 +1047,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'team_manager'}</t>
+          <t>team_manager</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Team Manager'}</t>
+          <t>Team Manager</t>
         </is>
       </c>
     </row>
@@ -1064,12 +1064,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'team_lead'}</t>
+          <t>team_lead</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Team Lead'}</t>
+          <t>Team Lead</t>
         </is>
       </c>
     </row>
@@ -1081,12 +1081,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1098,12 +1098,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1115,12 +1115,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1132,12 +1132,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'bi-weekly'}</t>
+          <t>bi-weekly</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Bi-Weekly'}</t>
+          <t>Bi-Weekly</t>
         </is>
       </c>
     </row>
@@ -1149,12 +1149,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1166,12 +1166,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'verbal'}</t>
+          <t>verbal</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Verbal'}</t>
+          <t>Verbal</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'written'}</t>
+          <t>written</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Written'}</t>
+          <t>Written</t>
         </is>
       </c>
     </row>
@@ -1200,12 +1200,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1217,12 +1217,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1234,12 +1234,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1251,12 +1251,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1268,12 +1268,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'prophets'}</t>
+          <t>prophets</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Prophets'}</t>
+          <t>Prophets</t>
         </is>
       </c>
     </row>
@@ -1285,12 +1285,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'shift_leader'}</t>
+          <t>shift_leader</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Shift Leader'}</t>
+          <t>Shift Leader</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'team_manager'}</t>
+          <t>team_manager</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Team Manager'}</t>
+          <t>Team Manager</t>
         </is>
       </c>
     </row>
@@ -1319,12 +1319,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'team_lead'}</t>
+          <t>team_lead</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Team Lead'}</t>
+          <t>Team Lead</t>
         </is>
       </c>
     </row>
@@ -1336,12 +1336,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1353,12 +1353,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'approved'}</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Approved'}</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -1370,12 +1370,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'in_review'}</t>
+          <t>in_review</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'In Review'}</t>
+          <t>In Review</t>
         </is>
       </c>
     </row>
@@ -1387,12 +1387,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'rejected'}</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Rejected'}</t>
+          <t>Rejected</t>
         </is>
       </c>
     </row>
@@ -1404,12 +1404,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
